--- a/gradebookproject/Community Feedback and Impact Gradebook.xlsx
+++ b/gradebookproject/Community Feedback and Impact Gradebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John\Desktop\rhode\freeCodeCampEXCEL\Project2_Gradebook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE844F6-0313-4B48-9EFA-41EF936F136C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635A08DE-8DDD-4453-871A-AE3726586A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31800" yWindow="1605" windowWidth="25170" windowHeight="15885" xr2:uid="{34259294-5C12-4B21-A099-97A8C650F262}"/>
+    <workbookView xWindow="2955" yWindow="1350" windowWidth="33240" windowHeight="15885" xr2:uid="{34259294-5C12-4B21-A099-97A8C650F262}"/>
   </bookViews>
   <sheets>
     <sheet name="Stanley Park Seawall" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>Stanley Park Seawall Proposal</t>
   </si>
@@ -106,12 +106,21 @@
   <si>
     <t>Project Impact Weights</t>
   </si>
+  <si>
+    <t>TOP RECOMMENDATIONS</t>
+  </si>
+  <si>
+    <t>#1 Choice:</t>
+  </si>
+  <si>
+    <t>#2 Choice:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +132,14 @@
       <sz val="10"/>
       <color rgb="FFC5C8C6"/>
       <name val="Inherit"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -147,10 +164,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -166,6 +183,2562 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Living Shoreline Reconnection</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$B$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Ecological Restoration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Intertidal Biodiversity</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Climate Resislance</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erosion Control</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Accessiblity </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Inclusivity</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cultural Resosnance</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Vistor-Nature Expereinces</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Recreation vs. Disruption</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Traffic Flow</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Trail Integration</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Stanley Park Seawall'!$B$2:$L$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9648-4D4A-A930-61BF0AB41552}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Layered Mobility Path System</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$B$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Ecological Restoration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Intertidal Biodiversity</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Climate Resislance</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erosion Control</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Accessiblity </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Inclusivity</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cultural Resosnance</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Vistor-Nature Expereinces</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Recreation vs. Disruption</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Traffic Flow</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Trail Integration</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Stanley Park Seawall'!$B$3:$L$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9648-4D4A-A930-61BF0AB41552}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Eco-Art Storyline Wall</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$B$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Ecological Restoration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Intertidal Biodiversity</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Climate Resislance</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erosion Control</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Accessiblity </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Inclusivity</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cultural Resosnance</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Vistor-Nature Expereinces</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Recreation vs. Disruption</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Traffic Flow</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Trail Integration</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Stanley Park Seawall'!$B$4:$L$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9648-4D4A-A930-61BF0AB41552}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tidal Amphitheatere and Learning Cove</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$B$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Ecological Restoration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Intertidal Biodiversity</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Climate Resislance</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erosion Control</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Accessiblity </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Inclusivity</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cultural Resosnance</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Vistor-Nature Expereinces</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Recreation vs. Disruption</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Traffic Flow</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Trail Integration</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Stanley Park Seawall'!$B$5:$L$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9648-4D4A-A930-61BF0AB41552}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Adaptive Elevation Pathway</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$B$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Ecological Restoration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Intertidal Biodiversity</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Climate Resislance</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erosion Control</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Accessiblity </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Inclusivity</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cultural Resosnance</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Vistor-Nature Expereinces</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Recreation vs. Disruption</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Traffic Flow</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Trail Integration</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Stanley Park Seawall'!$B$6:$L$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-9648-4D4A-A930-61BF0AB41552}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Wildlife Passage and Observation Zone</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$B$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Ecological Restoration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Intertidal Biodiversity</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Climate Resislance</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erosion Control</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Accessiblity </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Inclusivity</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cultural Resosnance</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Vistor-Nature Expereinces</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Recreation vs. Disruption</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Traffic Flow</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Trail Integration</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Stanley Park Seawall'!$B$7:$L$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-9648-4D4A-A930-61BF0AB41552}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Heritage Continuity Loop</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$B$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Ecological Restoration</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Intertidal Biodiversity</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Climate Resislance</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erosion Control</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Accessiblity </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Inclusivity</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Cultural Resosnance</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Vistor-Nature Expereinces</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Recreation vs. Disruption</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Traffic Flow</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Trail Integration</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Stanley Park Seawall'!$B$8:$L$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-9648-4D4A-A930-61BF0AB41552}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1205594720"/>
+        <c:axId val="471098752"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1205594720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="471098752"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="471098752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1205594720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.935870516185477E-2"/>
+          <c:y val="0.17171296296296298"/>
+          <c:w val="0.90930796150481186"/>
+          <c:h val="0.44347805482648001"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Rank</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Stanley Park Seawall'!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Living Shoreline Reconnection</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Layered Mobility Path System</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Eco-Art Storyline Wall</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tidal Amphitheatere and Learning Cove</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Adaptive Elevation Pathway</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Wildlife Passage and Observation Zone</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Heritage Continuity Loop</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Stanley Park Seawall'!$O$2:$O$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-073E-402C-9E86-DC07BA726B2D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="470188720"/>
+        <c:axId val="470190160"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="470188720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="470190160"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="470190160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="470188720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1038224</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>4761</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1602666-C25A-36AC-7356-1BAC297A8295}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE05141E-D449-0F8A-8CC2-792BF3D5518E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -501,7 +3074,7 @@
     <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -545,7 +3118,7 @@
       <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
       <c r="O1" t="s">
@@ -593,13 +3166,13 @@
         <f>AVERAGE(B2:L2)</f>
         <v>4.1818181818181817</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2">
         <f>SUMPRODUCT(B2:L2,$B$20:$L$20)</f>
         <v>4.3000000000000007</v>
       </c>
       <c r="O2">
-        <f>IFERROR(RANK(N3,$N$3:$N$9,0)+COUNTIF($N$3:N3,N3)-1, "Check Data")</f>
-        <v>3</v>
+        <f>IFERROR(RANK(N2,$N$2:$N$8,0),"Check Data")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -643,13 +3216,13 @@
         <f t="shared" ref="M3:M8" si="0">AVERAGE(B3:L3)</f>
         <v>4.0909090909090908</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3">
         <f t="shared" ref="N3:N8" si="1">SUMPRODUCT(B3:L3,$B$20:$L$20)</f>
         <v>4</v>
       </c>
       <c r="O3">
-        <f>IFERROR(RANK(N4,$N$3:$N$9,0)+COUNTIF($N$3:N4,N4)-1, "Check Data")</f>
-        <v>2</v>
+        <f t="shared" ref="O3:O8" si="2">IFERROR(RANK(N3,$N$2:$N$8,0),"Check Data")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -693,13 +3266,13 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N4">
         <f t="shared" si="1"/>
         <v>4.05</v>
       </c>
       <c r="O4">
-        <f>IFERROR(RANK(N5,$N$3:$N$9,0)+COUNTIF($N$3:N5,N5)-1, "Check Data")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -743,13 +3316,13 @@
         <f t="shared" si="0"/>
         <v>4.0909090909090908</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5">
         <f t="shared" si="1"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="O5">
-        <f>IFERROR(RANK(N6,$N$3:$N$9,0)+COUNTIF($N$3:N6,N6)-1, "Check Data")</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -793,13 +3366,13 @@
         <f t="shared" si="0"/>
         <v>3.9090909090909092</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="O6">
-        <f>IFERROR(RANK(N7,$N$3:$N$9,0)+COUNTIF($N$3:N7,N7)-1, "Check Data")</f>
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -843,13 +3416,13 @@
         <f t="shared" si="0"/>
         <v>3.5454545454545454</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7">
         <f t="shared" si="1"/>
         <v>3.75</v>
       </c>
       <c r="O7">
-        <f>IFERROR(RANK(N8,$N$3:$N$9,0)+COUNTIF($N$3:N8,N8)-1, "Check Data")</f>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -893,17 +3466,49 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8">
         <f t="shared" si="1"/>
         <v>3.85</v>
       </c>
-      <c r="O8" t="str">
-        <f>IFERROR(RANK(N9,$N$3:$N$9,0)+COUNTIF($N$3:N9,N9)-1, "Check Data")</f>
-        <v>Check Data</v>
+      <c r="O8">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="18.75">
+      <c r="A12" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="str">
+        <f>INDEX(A$2:A$8,MATCH(1,O$2:O$8,0))</f>
+        <v>Living Shoreline Reconnection</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <f>INDEX(N$2:N$8,MATCH(1,O$2:O$8,0))</f>
+        <v>4.3000000000000007</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="str">
+        <f>INDEX(A$2:A$8,MATCH(2,O$2:O$8,0))</f>
+        <v>Tidal Amphitheatere and Learning Cove</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B20">
@@ -946,5 +3551,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>